--- a/exam_forms/001_pharmacology_and_pathology_quiz--exam_forms.xlsx
+++ b/exam_forms/001_pharmacology_and_pathology_quiz--exam_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,13 +515,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is pharmacology</t>
+          <t>What is the definition of pharmacology?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -533,18 +533,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pathology_question_2</t>
+          <t>pharmacology_question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is pathology</t>
+          <t>What is the primary focus of pharmacology?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -556,18 +556,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>pharmacology_question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is the definition of pharmacology</t>
+          <t>What is the difference between a drug and a medication?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -584,13 +584,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is pharmacology related to</t>
+          <t>What is the role of pharmacology in treating diseases?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -602,18 +602,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pathology_question_5</t>
+          <t>pharmacology_question_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is pathology related to</t>
+          <t>What are some common pharmacological pathways involved in disease treatment?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -625,18 +625,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>pharmacology_question_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is the definition of pathology</t>
+          <t>What are the potential side effects of pharmacological interventions?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -648,12 +648,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pharmacology_question_7</t>
+          <t>pathology_question_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is pharmacology related to</t>
+          <t>What is the definition of pathology?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -671,12 +671,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pathology_question_8</t>
+          <t>pathology_question_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is pathology related to</t>
+          <t>What is the primary focus of pathology?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -694,12 +694,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_9</t>
+          <t>pathology_question_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is the definition of pharmacology</t>
+          <t>What is the difference between a disease and a condition?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_10</t>
+          <t>pathology_question_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is pharmacology related to</t>
+          <t>What is the role of pathology in diagnosing diseases?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -740,16 +740,85 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_11</t>
+          <t>pathology_question_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What is pharmacology</t>
+          <t>What are some common pathological processes involved in disease progression?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>pathology_question_6</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>What are the potential consequences of misdiagnosis in pathology?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>pharmacology_question_7</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>What is the relationship between pharmacology and pathology?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>pharmacology_question_8</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>How do pharmacological interventions impact pathology?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
